--- a/files/vegetable-recommendations.xlsx
+++ b/files/vegetable-recommendations.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jusep\Desktop\PROJECTS\amia-microsite.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19F285F-0D03-43B9-8678-A0516B392E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565D54EF-4341-41EE-B51C-3235AC1CAE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
+    <workbookView xWindow="7635" yWindow="2325" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
   </bookViews>
   <sheets>
     <sheet name="Vegetable_10Day(Municipal)" sheetId="9" r:id="rId1"/>
     <sheet name="Vegetable_10Day_SMS" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Vegetable_Seasonal(Provincial)" sheetId="13" r:id="rId3"/>
     <sheet name="Guidelines" sheetId="14" r:id="rId4"/>
-    <sheet name="Vegetable (General)" sheetId="6" state="hidden" r:id="rId5"/>
-    <sheet name="Vegetable_SMS" sheetId="3" state="hidden" r:id="rId6"/>
-    <sheet name="Vegetable_Special" sheetId="10" state="hidden" r:id="rId7"/>
-    <sheet name="Vegetable_Special_SMS" sheetId="12" state="hidden" r:id="rId8"/>
+    <sheet name="References" sheetId="16" r:id="rId5"/>
+    <sheet name="Vegetable (General)" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Vegetable_SMS" sheetId="3" state="hidden" r:id="rId7"/>
+    <sheet name="Vegetable_Special" sheetId="10" state="hidden" r:id="rId8"/>
+    <sheet name="Vegetable_Special_SMS" sheetId="12" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="132">
   <si>
     <t>Crop Stage</t>
   </si>
@@ -299,35 +300,672 @@
     <t>Maturing Stage</t>
   </si>
   <si>
-    <t>Favorable for trellis establishment</t>
-  </si>
-  <si>
-    <t>•	Nursery beds may develop cracks, reducing structural integrity.
-•	Shade materials (plastic/net) may become brittle under intense heat.
-•	Higher labor demand for frequent watering during establishment.
-•	Easier land clearing and bed formation.
-•	Lower risk of structural collapse from rain.
-•	No waterlogging risk during setup.</t>
-  </si>
-  <si>
-    <t>•	Compact bed edges properly to prevent crumbling.
-•	Incorporate high organic matter (compost, carbonized rice hull, coco coir) to improve moisture retention.
-•	Use windbreaks (banana trunks, netting, or bamboo slats) to reduce drying wind.
-•	Cover prepared beds with plastic sheet overnight to conserve moisture.
-•	Elevate nursery floor slightly to prevent future erosion.
-•	Avoid fully exposed open-field nursery during peak heat days.</t>
-  </si>
-  <si>
     <t>Preplanting  to Planting Stage</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>10-DAY WEATHER FORECAST</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ten(10) consecutive days with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">light rains </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or Five(5) consecutive days with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no rain</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Three(3) consecutive days with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">moderate rains </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or Two(2) consecutive days with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>heavy rains</t>
+    </r>
+  </si>
+  <si>
+    <t>SEASONAL FORECAST</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two(2) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">below normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(21% - 60% reduction from average) rainfall conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rainfall conditions are balanced</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and do not meet the threshold for water stress or flooding hazards during the 10-day forecast period</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two(2) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>above normal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (21% - 60% from average)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rainfall conditions are near normal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, without sustained anomalies of below normal or above normal rainfall</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Three(3) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">below normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(21% - 60% reduction from average) rainfall conditions;
+Two(2) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">way below normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(more than 60% reduction from average) rainfall conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Three(3) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>way</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">below normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(&gt;60% reduction from average);
+Five(5) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">below normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(21% - 60% reduction from average) rainfall condition</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Three(3) or more consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">above normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(&gt;60% increase from average);
+Two(2) consecutive months of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">way above normal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(more than 60% increase from average)</t>
+    </r>
+  </si>
+  <si>
+    <t>Nursery Establishment, Land Preparation, Seed Soaking , Mixing of Soil Media, Seed Sowing, Transplanting, Nutrient Management, Trellis Establishment</t>
+  </si>
+  <si>
+    <t>CROP STAGES</t>
+  </si>
+  <si>
+    <t>FARMING ACTIVITIES</t>
+  </si>
+  <si>
+    <t>Water Management, Pest Management, Nutrient Management, Trellis Management</t>
+  </si>
+  <si>
+    <t>Water Management, Pest Management, Nutrient Management, Fruit Bagging</t>
+  </si>
+  <si>
+    <t>Fruit/Leaves Thinning, Nutrient Management</t>
+  </si>
+  <si>
+    <t>Harvesting, Post Harvest Management</t>
+  </si>
+  <si>
+    <t>IMPACT OUTLOOK AND MANAGEMENT RECOMMENDATION GUIDELINES</t>
+  </si>
+  <si>
+    <t>1. Provide recommendations for every farm activity listed under each climate risk.</t>
+  </si>
+  <si>
+    <t>• Proceed with planned nursery bed preparation schedule.
+• Maintain proper bed compaction to ensure stability.
+• Install standard drainage as precautionary measure.
+• Monitor daily weather updates for sudden forecast changes.
+• Maintain moderate watering schedule to prevent over- or under-moistening.</t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Do not leave any cell blank.</t>
+  </si>
+  <si>
+    <t>- All fields for Impact Outlook and Management Recommendation must be completed.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Negative Impact:
+• Nursery beds may dry rapidly, causing cracking.
+• Increased labor requirement for frequent watering.
+• Higher surface temperature may weaken shade materials.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A6F00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Positive Impact:
+• Easier bed shaping and soil pulverization.
+• No risk of waterlogging during bed preparation.
+• Lower fungal contamination risk compared to wet conditions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Negative Impact:
+• Newly prepared nursery beds may become saturated within 24–48 hours.
+• Temporary ponding may weaken bed edges and cause partial erosion.
+• High humidity may favor early fungal contamination of nursery media.
+• Installation of shade structures may be delayed due to muddy ground conditions.
+• Movement of materials and labor efficiency may be reduced.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A6F00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Positive Impact:
+• Increased soil moisture may reduce initial watering requirements.
+• Rainfall may help settle and compact newly prepared nursery beds naturally.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>• Incorporate organic matter to improve moisture retention.
+• Schedule watering during early morning or late afternoon.
+• Use temporary windbreaks to reduce drying effect.
+• Complete bed formation and structural reinforcement during dry window.
+• Install drainage layout while soil is workable.</t>
+    </r>
+  </si>
+  <si>
+    <t>• Construct shallow drainage canals before expected heavy rainfall.
+• Elevate nursery beds at least 15–20 cm above ground level.
+• Avoid preparing beds immediately before forecasted heavy rain days.
+• Cover prepared beds with plastic sheets during intense rainfall events.
+• Store seedling trays and media in a protected, elevated area.
+• Inspect nursery site immediately after rainfall and repair eroded edges.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Negative Impact:
+• 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A6F00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Positive Impact:
+• Soil moisture remains adequate for bed preparation.
+• Low likelihood of structural damage from rainfall.
+• Minimal interruption to nursery construction activities.
+• Stable working conditions for installation of shade structures.</t>
+    </r>
+  </si>
+  <si>
+    <t>- All Impact Outlook and Management Recommendation fields must be completed, and no cell should be left blank</t>
+  </si>
+  <si>
+    <t>- Each farm activity must have at least one management recommendation tailored to the specific climate condition and corresponding impact outlook.</t>
+  </si>
+  <si>
+    <t>2. Ensure alignment between climate risk, impact outlook, and recommendation.</t>
+  </si>
+  <si>
+    <t>- Impact outlooks must directly relate to the specified climate risk and include both negative and positive effects where applicable</t>
+  </si>
+  <si>
+    <t>- Recommendations must directly respond to the stated impacts</t>
+  </si>
+  <si>
+    <t>- Multiple recommendations may be provided if necessary</t>
+  </si>
+  <si>
+    <t>3. Provide detailed, practical, and farmer-level applicable management recommendations.</t>
+  </si>
+  <si>
+    <t>- Avoid vague instructions unless paired with a clear and actionable measure</t>
+  </si>
+  <si>
+    <t>5. Climate risks are standardized and fixed. Do not add, remove, or modify the provided climate risk categories.</t>
+  </si>
+  <si>
+    <t>6. Include crop insurance (PCIC) recommendations where appropriate, particularly during vulnerable crop stages such as flowering or fruiting.</t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Recommend PCIC crop insurance enrollment during reproductive and maturing stages for high-value crops.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Instead of “monitor plants,” use “monitor plants for pest infestation and apply neem extract if early pest signs are observed.”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If flooding risk may cause soil erosion, recommend elevated nursery beds or drainage construction.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If the farm activity is nursery establishment under water shortage risk, provide recommendations such as improved moisture conservation techniques.</t>
+    </r>
+  </si>
+  <si>
+    <t>Preplanting Preparation to Planting Stage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -447,8 +1085,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A6F00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +1152,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -510,171 +1183,232 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="8">
+    <cellStyle name="20% - Accent6" xfId="6" builtinId="50"/>
+    <cellStyle name="20% - Accent6 2" xfId="7" xr:uid="{052B44E9-0A15-4AB2-AF9A-CE4EC45D892E}"/>
     <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
     <cellStyle name="40% - Accent2" xfId="2" builtinId="35"/>
     <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
@@ -998,8 +1732,11 @@
     <col min="1" max="1" width="27.375" style="17" customWidth="1"/>
     <col min="2" max="2" width="33.25" style="17" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="17" customWidth="1"/>
-    <col min="4" max="4" width="39.625" style="17" customWidth="1"/>
-    <col min="5" max="8" width="32.875" style="17" customWidth="1"/>
+    <col min="4" max="4" width="43.125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="39.625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="17" customWidth="1"/>
+    <col min="8" max="8" width="32.875" style="17" customWidth="1"/>
     <col min="9" max="9" width="22.625" style="4" customWidth="1"/>
     <col min="10" max="16384" width="11" style="4"/>
   </cols>
@@ -1014,14 +1751,14 @@
       <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1042,29 +1779,29 @@
       </c>
       <c r="I2" s="32"/>
     </row>
-    <row r="3" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="50" t="s">
+    <row r="3" spans="1:9" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>77</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>69</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="30"/>
+        <v>112</v>
+      </c>
+      <c r="E3" s="56"/>
       <c r="F3" s="46" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G3" s="30"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="288" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>77</v>
@@ -1072,15 +1809,19 @@
       <c r="C4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+      <c r="D4" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="56"/>
+      <c r="F4" s="66" t="s">
+        <v>115</v>
+      </c>
       <c r="G4" s="30"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="272.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>77</v>
@@ -1088,17 +1829,21 @@
       <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="D5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="56"/>
+      <c r="F5" s="66" t="s">
+        <v>108</v>
+      </c>
       <c r="G5" s="30"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="69" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="30" t="s">
@@ -1112,7 +1857,7 @@
     </row>
     <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>71</v>
@@ -1128,7 +1873,7 @@
     </row>
     <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B8" s="30" t="s">
         <v>71</v>
@@ -1144,9 +1889,9 @@
     </row>
     <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="69" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -1160,7 +1905,7 @@
     </row>
     <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="42" t="s">
         <v>78</v>
@@ -1176,7 +1921,7 @@
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="42" t="s">
         <v>78</v>
@@ -1192,9 +1937,9 @@
     </row>
     <row r="12" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="69" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -1208,7 +1953,7 @@
     </row>
     <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>72</v>
@@ -1224,7 +1969,7 @@
     </row>
     <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" s="30" t="s">
         <v>72</v>
@@ -1240,9 +1985,9 @@
     </row>
     <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="69" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="30" t="s">
@@ -1256,7 +2001,7 @@
     </row>
     <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>73</v>
@@ -1272,7 +2017,7 @@
     </row>
     <row r="17" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>73</v>
@@ -1288,9 +2033,9 @@
     </row>
     <row r="18" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="69" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="30" t="s">
@@ -1304,7 +2049,7 @@
     </row>
     <row r="19" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B19" s="30" t="s">
         <v>74</v>
@@ -1320,7 +2065,7 @@
     </row>
     <row r="20" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>74</v>
@@ -1336,9 +2081,9 @@
     </row>
     <row r="21" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="69" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="30" t="s">
@@ -1352,7 +2097,7 @@
     </row>
     <row r="22" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>13</v>
@@ -1368,7 +2113,7 @@
     </row>
     <row r="23" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" s="47" t="s">
         <v>13</v>
@@ -1384,17 +2129,15 @@
     </row>
     <row r="24" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="69" t="s">
         <v>79</v>
       </c>
       <c r="C24" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="46" t="s">
-        <v>85</v>
-      </c>
+      <c r="D24" s="46"/>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="30"/>
@@ -1402,7 +2145,7 @@
     </row>
     <row r="25" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B25" s="42" t="s">
         <v>79</v>
@@ -1418,7 +2161,7 @@
     </row>
     <row r="26" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B26" s="42" t="s">
         <v>79</v>
@@ -1426,9 +2169,7 @@
       <c r="C26" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="46" t="s">
-        <v>85</v>
-      </c>
+      <c r="D26" s="46"/>
       <c r="E26" s="30"/>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
@@ -1438,7 +2179,7 @@
       <c r="A27" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="70" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="29" t="s">
@@ -1486,7 +2227,7 @@
       <c r="A30" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="70" t="s">
         <v>67</v>
       </c>
       <c r="C30" s="29" t="s">
@@ -1582,7 +2323,7 @@
       <c r="A36" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="70" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="29" t="s">
@@ -1630,7 +2371,7 @@
       <c r="A39" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="71" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="26" t="s">
@@ -1774,7 +2515,7 @@
       <c r="A48" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="49" t="s">
+      <c r="B48" s="71" t="s">
         <v>82</v>
       </c>
       <c r="C48" s="26" t="s">
@@ -1822,7 +2563,7 @@
       <c r="A51" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="44" t="s">
+      <c r="B51" s="72" t="s">
         <v>81</v>
       </c>
       <c r="C51" s="28" t="s">
@@ -1867,7 +2608,7 @@
       <c r="A54" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="44" t="s">
+      <c r="B54" s="72" t="s">
         <v>13</v>
       </c>
       <c r="C54" s="28" t="s">
@@ -1942,7 +2683,7 @@
       <c r="A59" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="54" t="s">
         <v>14</v>
       </c>
       <c r="C59" s="27" t="s">
@@ -1957,7 +2698,7 @@
       <c r="A60" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="54" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="27" t="s">
@@ -2653,14 +3394,14 @@
       <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="58"/>
       <c r="H1" s="11"/>
       <c r="I1" s="14"/>
     </row>
@@ -2685,7 +3426,7 @@
     </row>
     <row r="3" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>77</v>
@@ -2703,7 +3444,7 @@
     </row>
     <row r="4" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>77</v>
@@ -2721,7 +3462,7 @@
     </row>
     <row r="5" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>77</v>
@@ -2739,7 +3480,7 @@
     </row>
     <row r="6" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>77</v>
@@ -2757,7 +3498,7 @@
     </row>
     <row r="7" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" s="42" t="s">
         <v>77</v>
@@ -2775,7 +3516,7 @@
     </row>
     <row r="8" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>77</v>
@@ -2793,7 +3534,7 @@
     </row>
     <row r="9" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>71</v>
@@ -2811,7 +3552,7 @@
     </row>
     <row r="10" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>71</v>
@@ -2829,7 +3570,7 @@
     </row>
     <row r="11" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>71</v>
@@ -2847,7 +3588,7 @@
     </row>
     <row r="12" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>71</v>
@@ -2865,7 +3606,7 @@
     </row>
     <row r="13" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B13" s="30" t="s">
         <v>71</v>
@@ -2883,7 +3624,7 @@
     </row>
     <row r="14" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" s="30" t="s">
         <v>71</v>
@@ -2901,7 +3642,7 @@
     </row>
     <row r="15" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>78</v>
@@ -2919,7 +3660,7 @@
     </row>
     <row r="16" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>78</v>
@@ -2937,7 +3678,7 @@
     </row>
     <row r="17" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>78</v>
@@ -2955,7 +3696,7 @@
     </row>
     <row r="18" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" s="42" t="s">
         <v>78</v>
@@ -2973,7 +3714,7 @@
     </row>
     <row r="19" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>78</v>
@@ -2991,7 +3732,7 @@
     </row>
     <row r="20" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>78</v>
@@ -3009,7 +3750,7 @@
     </row>
     <row r="21" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="30" t="s">
         <v>72</v>
@@ -3027,7 +3768,7 @@
     </row>
     <row r="22" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>72</v>
@@ -3045,7 +3786,7 @@
     </row>
     <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>72</v>
@@ -3063,7 +3804,7 @@
     </row>
     <row r="24" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" s="30" t="s">
         <v>72</v>
@@ -3081,7 +3822,7 @@
     </row>
     <row r="25" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B25" s="30" t="s">
         <v>72</v>
@@ -3099,7 +3840,7 @@
     </row>
     <row r="26" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>72</v>
@@ -3117,7 +3858,7 @@
     </row>
     <row r="27" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B27" s="30" t="s">
         <v>73</v>
@@ -3135,7 +3876,7 @@
     </row>
     <row r="28" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>73</v>
@@ -3153,7 +3894,7 @@
     </row>
     <row r="29" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" s="30" t="s">
         <v>73</v>
@@ -3171,7 +3912,7 @@
     </row>
     <row r="30" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" s="30" t="s">
         <v>73</v>
@@ -3189,7 +3930,7 @@
     </row>
     <row r="31" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>73</v>
@@ -3207,7 +3948,7 @@
     </row>
     <row r="32" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>73</v>
@@ -3225,7 +3966,7 @@
     </row>
     <row r="33" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>74</v>
@@ -3243,7 +3984,7 @@
     </row>
     <row r="34" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>74</v>
@@ -3261,7 +4002,7 @@
     </row>
     <row r="35" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B35" s="30" t="s">
         <v>74</v>
@@ -3279,7 +4020,7 @@
     </row>
     <row r="36" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B36" s="30" t="s">
         <v>74</v>
@@ -3297,7 +4038,7 @@
     </row>
     <row r="37" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>74</v>
@@ -3315,7 +4056,7 @@
     </row>
     <row r="38" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B38" s="30" t="s">
         <v>74</v>
@@ -3333,7 +4074,7 @@
     </row>
     <row r="39" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B39" s="47" t="s">
         <v>13</v>
@@ -3351,7 +4092,7 @@
     </row>
     <row r="40" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B40" s="47" t="s">
         <v>13</v>
@@ -3369,7 +4110,7 @@
     </row>
     <row r="41" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B41" s="47" t="s">
         <v>13</v>
@@ -3387,7 +4128,7 @@
     </row>
     <row r="42" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B42" s="47" t="s">
         <v>13</v>
@@ -3405,7 +4146,7 @@
     </row>
     <row r="43" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B43" s="47" t="s">
         <v>13</v>
@@ -3423,7 +4164,7 @@
     </row>
     <row r="44" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B44" s="47" t="s">
         <v>13</v>
@@ -3441,7 +4182,7 @@
     </row>
     <row r="45" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B45" s="47" t="s">
         <v>79</v>
@@ -3459,7 +4200,7 @@
     </row>
     <row r="46" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B46" s="47" t="s">
         <v>79</v>
@@ -3477,7 +4218,7 @@
     </row>
     <row r="47" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B47" s="47" t="s">
         <v>79</v>
@@ -3495,7 +4236,7 @@
     </row>
     <row r="48" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B48" s="47" t="s">
         <v>79</v>
@@ -3513,7 +4254,7 @@
     </row>
     <row r="49" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B49" s="47" t="s">
         <v>79</v>
@@ -3531,7 +4272,7 @@
     </row>
     <row r="50" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B50" s="47" t="s">
         <v>79</v>
@@ -4757,14 +5498,450 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A4C548-7A31-4848-A85E-56BF26149FA7}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="6" width="19.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+    </row>
+    <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+    </row>
+    <row r="4" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+    </row>
+    <row r="42" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A15:H15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5B4BB0-127B-47A1-8C0E-754FAF9D6D3C}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="2" max="2" width="86.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="68"/>
+    </row>
+    <row r="11" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="68"/>
+    </row>
+    <row r="17" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A16:B16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B020F0C-4030-5B4A-A41A-388920D315A9}">
   <dimension ref="A1:G83"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -4780,14 +5957,14 @@
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="52"/>
+      <c r="E1" s="64"/>
       <c r="F1" s="11"/>
       <c r="G1" s="14"/>
     </row>
@@ -5593,7 +6770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D34D3AE-F2E2-3348-B195-43FB4D0F780C}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5805,7 +6982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B4F791-8893-1849-9452-A54B8C2F2F8E}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5821,14 +6998,14 @@
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="53"/>
+      <c r="E1" s="65"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="20"/>
@@ -6026,7 +7203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51686372-B2DE-1B43-8972-F1AC9C8B5F60}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/files/vegetable-recommendations.xlsx
+++ b/files/vegetable-recommendations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jusep\Desktop\PROJECTS\amia-microsite.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565D54EF-4341-41EE-B51C-3235AC1CAE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F444883F-A38C-4EC9-87CD-A4C66B347810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7635" yWindow="2325" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
   </bookViews>
   <sheets>
     <sheet name="Vegetable_10Day(Municipal)" sheetId="9" r:id="rId1"/>
@@ -1193,7 +1193,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1360,38 +1360,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="7" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="7" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1404,6 +1377,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="7" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1751,14 +1754,14 @@
       <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="64"/>
       <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,7 +1786,7 @@
       <c r="A3" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="60" t="s">
         <v>77</v>
       </c>
       <c r="C3" s="30" t="s">
@@ -1813,7 +1816,7 @@
         <v>113</v>
       </c>
       <c r="E4" s="56"/>
-      <c r="F4" s="66" t="s">
+      <c r="F4" s="58" t="s">
         <v>115</v>
       </c>
       <c r="G4" s="30"/>
@@ -1833,7 +1836,7 @@
         <v>116</v>
       </c>
       <c r="E5" s="56"/>
-      <c r="F5" s="66" t="s">
+      <c r="F5" s="58" t="s">
         <v>108</v>
       </c>
       <c r="G5" s="30"/>
@@ -1843,7 +1846,7 @@
       <c r="A6" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="60" t="s">
         <v>71</v>
       </c>
       <c r="C6" s="30" t="s">
@@ -1891,7 +1894,7 @@
       <c r="A9" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="60" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -1939,7 +1942,7 @@
       <c r="A12" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="60" t="s">
         <v>72</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -1987,7 +1990,7 @@
       <c r="A15" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="60" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="30" t="s">
@@ -2035,7 +2038,7 @@
       <c r="A18" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="60" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="30" t="s">
@@ -2083,7 +2086,7 @@
       <c r="A21" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="60" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="30" t="s">
@@ -2131,7 +2134,7 @@
       <c r="A24" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="60" t="s">
         <v>79</v>
       </c>
       <c r="C24" s="30" t="s">
@@ -2179,7 +2182,7 @@
       <c r="A27" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="61" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="29" t="s">
@@ -2227,7 +2230,7 @@
       <c r="A30" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="61" t="s">
         <v>67</v>
       </c>
       <c r="C30" s="29" t="s">
@@ -2323,7 +2326,7 @@
       <c r="A36" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="61" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="29" t="s">
@@ -2371,7 +2374,7 @@
       <c r="A39" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="71" t="s">
+      <c r="B39" s="62" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="26" t="s">
@@ -2515,7 +2518,7 @@
       <c r="A48" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="71" t="s">
+      <c r="B48" s="62" t="s">
         <v>82</v>
       </c>
       <c r="C48" s="26" t="s">
@@ -2563,7 +2566,7 @@
       <c r="A51" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="B51" s="72" t="s">
+      <c r="B51" s="63" t="s">
         <v>81</v>
       </c>
       <c r="C51" s="28" t="s">
@@ -2608,7 +2611,7 @@
       <c r="A54" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="B54" s="72" t="s">
+      <c r="B54" s="63" t="s">
         <v>13</v>
       </c>
       <c r="C54" s="28" t="s">
@@ -3394,14 +3397,14 @@
       <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="64"/>
+      <c r="F1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="58"/>
+      <c r="G1" s="64"/>
       <c r="H1" s="11"/>
       <c r="I1" s="14"/>
     </row>
@@ -5506,16 +5509,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
       <c r="J1" s="52"/>
       <c r="K1" s="52"/>
       <c r="L1" s="52"/>
@@ -5526,16 +5529,16 @@
       <c r="Q1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
       <c r="J2" s="55"/>
       <c r="K2" s="55"/>
       <c r="L2" s="55"/>
@@ -5546,162 +5549,162 @@
       <c r="Q2" s="55"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B39" s="57"/>
@@ -5713,26 +5716,26 @@
       <c r="H39" s="57"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="61" t="s">
+      <c r="B41" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
     </row>
     <row r="42" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A42" s="57" t="s">
@@ -5742,9 +5745,6 @@
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B24:H24"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B40:H40"/>
@@ -5760,6 +5760,9 @@
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B24:H24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5775,10 +5778,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="59" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5830,10 +5833,10 @@
     </row>
     <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="71"/>
     </row>
     <row r="11" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="51" t="s">
@@ -5869,10 +5872,10 @@
     </row>
     <row r="15" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="71"/>
     </row>
     <row r="17" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
@@ -5957,14 +5960,14 @@
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="64"/>
+      <c r="E1" s="72"/>
       <c r="F1" s="11"/>
       <c r="G1" s="14"/>
     </row>
@@ -6998,14 +7001,14 @@
       <c r="A1" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="65"/>
+      <c r="E1" s="73"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="20"/>

--- a/files/vegetable-recommendations.xlsx
+++ b/files/vegetable-recommendations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jusep\Desktop\PROJECTS\amia-microsite.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F444883F-A38C-4EC9-87CD-A4C66B347810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4AC212-5839-4C1A-9B35-29F29CC581F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{E2D1DC89-D079-3B4D-864B-8CE149E3E279}"/>
   </bookViews>
   <sheets>
     <sheet name="Vegetable_10Day(Municipal)" sheetId="9" r:id="rId1"/>
@@ -828,35 +828,6 @@
     <t>5. Climate risks are standardized and fixed. Do not add, remove, or modify the provided climate risk categories.</t>
   </si>
   <si>
-    <t>6. Include crop insurance (PCIC) recommendations where appropriate, particularly during vulnerable crop stages such as flowering or fruiting.</t>
-  </si>
-  <si>
-    <r>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>x.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Recommend PCIC crop insurance enrollment during reproductive and maturing stages for high-value crops.</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t>e</t>
     </r>
@@ -936,6 +907,35 @@
   </si>
   <si>
     <t>Preplanting Preparation to Planting Stage</t>
+  </si>
+  <si>
+    <t>6. Include crop insurance (PCIC) recommendations where appropriate.</t>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>x.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Apply for PCIC crop insurance before planting and within 20 days after planting</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" s="68"/>
       <c r="D6" s="68"/>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="66" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="69" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B23" s="69"/>
       <c r="C23" s="69"/>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" s="66" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
@@ -5745,6 +5745,8 @@
     <row r="45" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B24:H24"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B40:H40"/>
@@ -5761,8 +5763,6 @@
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B24:H24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5787,7 +5787,7 @@
     </row>
     <row r="2" spans="1:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>99</v>
